--- a/results/Int Task Remove ACC -1.0/Rando_6_permute.xlsx
+++ b/results/Int Task Remove ACC -1.0/Rando_6_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6164097979902786</v>
+        <v>0.6130669800703961</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6158526949262118</v>
+        <v>0.6139423422272948</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6130669800703961</v>
+        <v>0.6152951927911822</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6130669800703961</v>
+        <v>0.6236916458484648</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6107984611823675</v>
+        <v>0.6236916458484648</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.6113555642464343</v>
+        <v>0.6250446959478334</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6114351789035126</v>
+        <v>0.6232141574414762</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6189963764356577</v>
+        <v>0.6189558707329337</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.6193545426247695</v>
+        <v>0.6161699563416366</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.6189963764356577</v>
+        <v>0.6195919898476347</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.6109177834002443</v>
+        <v>0.6292227693928534</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.6060225794350751</v>
+        <v>0.6302972679601886</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.6033563863326177</v>
+        <v>0.6302972679601886</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.6048283595789004</v>
+        <v>0.6355901461397866</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6111955367903521</v>
+        <v>0.6365852295855249</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6065790838926979</v>
+        <v>0.6596275869775163</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6057835359283588</v>
+        <v>0.659349035445483</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6059824728033139</v>
+        <v>0.6639253817113759</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6093649982839948</v>
+        <v>0.6761038302831009</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6070170642743693</v>
+        <v>0.6761038302831009</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6037135548443224</v>
+        <v>0.6673893176684678</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6002510156356003</v>
+        <v>0.6673893176684678</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.6020021390203606</v>
+        <v>0.6726438850356371</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.587755106112969</v>
+        <v>0.6665552593562187</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5845316104109632</v>
+        <v>0.6762662521649601</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5622855991252365</v>
+        <v>0.6665165494728273</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5637182638816834</v>
+        <v>0.6545386340599085</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.5571920568915565</v>
+        <v>0.6457045996919173</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5515013049620483</v>
+        <v>0.6375479882832765</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.5556003623564342</v>
+        <v>0.6079874053204141</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5556003623564342</v>
+        <v>0.6107332130799499</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5475622750237447</v>
+        <v>0.6096190069518161</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5521783288504362</v>
+        <v>0.6028150465715814</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.5975095976566553</v>
+        <v>0.5771916977276899</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.5840577136426399</v>
+        <v>0.5672835638633262</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.5860071752959111</v>
+        <v>0.5433672410628058</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5713225610778109</v>
+        <v>0.532624051208786</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.6041162174457863</v>
+        <v>0.5308332202632272</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5895894357934728</v>
+        <v>0.5274109872217477</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5884752296653391</v>
+        <v>0.555743628832079</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6328491272318044</v>
+        <v>0.5469518959861442</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.620830905651643</v>
+        <v>0.5415410923370394</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5925391688149987</v>
+        <v>0.5349348716188713</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5976736158223654</v>
+        <v>0.534616412990558</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6142270793592517</v>
+        <v>0.5469121884253458</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.6155011134079862</v>
+        <v>0.546355085361279</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.6204356258629909</v>
+        <v>0.5737722581829501</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.6291525329034009</v>
+        <v>0.5213642639934233</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6291525329034009</v>
+        <v>0.4992782801637787</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5874067171624457</v>
+        <v>0.4956170036155829</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5708133465292798</v>
+        <v>0.4902451093853509</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5564066852367688</v>
+        <v>0.4859064098778045</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5029265869056836</v>
+        <v>0.4787825941208866</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5010565403740093</v>
+        <v>0.4662846892434413</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5564880957131797</v>
+        <v>0.4653297124294642</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5731626772872752</v>
+        <v>0.500392286756431</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5592353002210853</v>
+        <v>0.4923534012818159</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5592353002210853</v>
+        <v>0.4800195145700809</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5921859910129219</v>
+        <v>0.4710244550686003</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.570976367017583</v>
+        <v>0.4650958568452642</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6033312448619613</v>
+        <v>0.464698980772761</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6043259292367369</v>
+        <v>0.4705888691127056</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5760746981028166</v>
+        <v>0.4705888691127056</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5713421155549879</v>
+        <v>0.4725786369332194</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5621910193070532</v>
+        <v>0.472420006225507</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.577349131222514</v>
+        <v>0.4663297842622375</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5845938654811599</v>
+        <v>0.4534761076214572</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5632663160163141</v>
+        <v>0.4529589116536702</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5522834840491336</v>
+        <v>0.4500933826052949</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5499738608519367</v>
+        <v>0.4923581901333695</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5436096766727059</v>
+        <v>0.4964963564821097</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5047748840698854</v>
+        <v>0.4957008085177706</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5050534356019187</v>
+        <v>0.4957008085177706</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5048944058232435</v>
+        <v>0.4988049820018996</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5048944058232435</v>
+        <v>0.500397275143466</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.5031037744131661</v>
+        <v>0.5026258869352148</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5033823259451996</v>
+        <v>0.5023078273778644</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5033823259451996</v>
+        <v>0.501073899960891</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5038598143521881</v>
+        <v>0.4985667366371088</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5020691829421108</v>
+        <v>0.4987261654867469</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5016713091922006</v>
+        <v>0.4991240392366571</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5011142061281337</v>
+        <v>0.4991240392366571</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5005571030640669</v>
+        <v>0.4998006640540821</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5011142061281337</v>
+        <v>0.4996416342754069</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5011142061281337</v>
+        <v>0.4993630827433734</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5001989368749551</v>
+        <v>0.4996813418362053</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5</v>
+        <v>0.4996813418362053</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5</v>
+        <v>0.5013123448611632</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4994826044967316</v>
+        <v>0.5012333288105291</v>
       </c>
     </row>
   </sheetData>
